--- a/DocumentosProceso/Comprobación para el reembolso de fondo fijo de CEDIS.xlsx
+++ b/DocumentosProceso/Comprobación para el reembolso de fondo fijo de CEDIS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t>COMPROBACIÓN PARA EL REEMBOLSO DE FONDO FIJO DE CEDIS</t>
   </si>
@@ -46,6 +46,9 @@
   </si>
   <si>
     <t>Proveedor</t>
+  </si>
+  <si>
+    <t>Descripción</t>
   </si>
   <si>
     <t>Concepto del gasto</t>
@@ -98,7 +101,7 @@
     <numFmt numFmtId="166" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -144,6 +147,11 @@
       <sz val="10.0"/>
       <color theme="0"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="7.0"/>
@@ -241,6 +249,38 @@
       <right style="thin">
         <color rgb="FF7F7F7F"/>
       </right>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
         <color rgb="FF7F7F7F"/>
       </top>
@@ -276,17 +316,6 @@
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
       <top style="thin">
         <color rgb="FF7F7F7F"/>
       </top>
@@ -299,32 +328,11 @@
         <color rgb="FF7F7F7F"/>
       </top>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-    </border>
-    <border>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="42">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -336,11 +344,11 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
@@ -375,49 +383,56 @@
     <xf borderId="9" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="10" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="11" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="12" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="13" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="7" numFmtId="15" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="7" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="13" fillId="0" fontId="7" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="7" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="13" fillId="0" fontId="7" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="14" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="14" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="15" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="7" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf borderId="13" fillId="0" fontId="7" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="12" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="16" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="13" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="14" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="0" fontId="7" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="17" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="15" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="18" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="16" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="17" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="18" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -686,15 +701,15 @@
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
       <c r="N1" s="3"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="5" t="s">
+      <c r="O1" s="3"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="Q1" s="6">
+      <c r="S1" s="5">
         <v>1.0</v>
       </c>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
       <c r="T1" s="7"/>
       <c r="U1" s="7"/>
       <c r="V1" s="7"/>
@@ -870,10 +885,9 @@
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="4"/>
       <c r="U7" s="7"/>
       <c r="V7" s="7"/>
       <c r="W7" s="7"/>
@@ -885,39 +899,40 @@
       <c r="A8" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="9" t="s">
+      <c r="C8" s="21"/>
+      <c r="D8" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="9" t="s">
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="12"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="21"/>
       <c r="L8" s="9" t="s">
         <v>11</v>
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="12"/>
-      <c r="O8" s="19" t="s">
+      <c r="O8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="P8" s="19" t="s">
+      <c r="P8" s="12"/>
+      <c r="Q8" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="Q8" s="19" t="s">
+      <c r="R8" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="R8" s="7"/>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
+      <c r="S8" s="19" t="s">
+        <v>15</v>
+      </c>
       <c r="U8" s="7"/>
       <c r="V8" s="7"/>
       <c r="W8" s="7"/>
@@ -926,10 +941,10 @@
       <c r="Z8" s="7"/>
     </row>
     <row r="9" ht="18.0" customHeight="1">
-      <c r="A9" s="20">
+      <c r="A9" s="23">
         <v>1.0</v>
       </c>
-      <c r="B9" s="21"/>
+      <c r="B9" s="24"/>
       <c r="C9" s="12"/>
       <c r="D9" s="15"/>
       <c r="E9" s="10"/>
@@ -939,22 +954,21 @@
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
       <c r="K9" s="12"/>
-      <c r="L9" s="15"/>
+      <c r="L9" s="25"/>
       <c r="M9" s="10"/>
       <c r="N9" s="12"/>
-      <c r="O9" s="22">
+      <c r="O9" s="15"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="26">
         <v>0.0</v>
       </c>
-      <c r="P9" s="22">
+      <c r="R9" s="26">
         <v>0.0</v>
       </c>
-      <c r="Q9" s="23">
-        <f t="shared" ref="Q9:Q28" si="1">O9+P9</f>
+      <c r="S9" s="27">
+        <f t="shared" ref="S9:S28" si="1">Q9+R9</f>
         <v>0</v>
       </c>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
       <c r="U9" s="7"/>
       <c r="V9" s="7"/>
       <c r="W9" s="7"/>
@@ -963,10 +977,10 @@
       <c r="Z9" s="7"/>
     </row>
     <row r="10" ht="18.0" customHeight="1">
-      <c r="A10" s="20">
+      <c r="A10" s="23">
         <v>2.0</v>
       </c>
-      <c r="B10" s="21"/>
+      <c r="B10" s="24"/>
       <c r="C10" s="12"/>
       <c r="D10" s="15"/>
       <c r="E10" s="10"/>
@@ -976,22 +990,21 @@
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
       <c r="K10" s="12"/>
-      <c r="L10" s="15"/>
+      <c r="L10" s="25"/>
       <c r="M10" s="10"/>
       <c r="N10" s="12"/>
-      <c r="O10" s="23">
+      <c r="O10" s="15"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="27">
         <v>0.0</v>
       </c>
-      <c r="P10" s="23">
+      <c r="R10" s="27">
         <v>0.0</v>
       </c>
-      <c r="Q10" s="23">
+      <c r="S10" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R10" s="7"/>
-      <c r="S10" s="7"/>
-      <c r="T10" s="7"/>
       <c r="U10" s="7"/>
       <c r="V10" s="7"/>
       <c r="W10" s="7"/>
@@ -1000,10 +1013,10 @@
       <c r="Z10" s="7"/>
     </row>
     <row r="11" ht="18.0" customHeight="1">
-      <c r="A11" s="20">
+      <c r="A11" s="23">
         <v>3.0</v>
       </c>
-      <c r="B11" s="21"/>
+      <c r="B11" s="24"/>
       <c r="C11" s="12"/>
       <c r="D11" s="15"/>
       <c r="E11" s="10"/>
@@ -1013,22 +1026,21 @@
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
       <c r="K11" s="12"/>
-      <c r="L11" s="15"/>
+      <c r="L11" s="25"/>
       <c r="M11" s="10"/>
       <c r="N11" s="12"/>
-      <c r="O11" s="23">
+      <c r="O11" s="15"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="27">
         <v>0.0</v>
       </c>
-      <c r="P11" s="23">
+      <c r="R11" s="27">
         <v>0.0</v>
       </c>
-      <c r="Q11" s="23">
+      <c r="S11" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R11" s="7"/>
-      <c r="S11" s="7"/>
-      <c r="T11" s="7"/>
       <c r="U11" s="7"/>
       <c r="V11" s="7"/>
       <c r="W11" s="7"/>
@@ -1037,10 +1049,10 @@
       <c r="Z11" s="7"/>
     </row>
     <row r="12" ht="18.0" customHeight="1">
-      <c r="A12" s="20">
+      <c r="A12" s="23">
         <v>4.0</v>
       </c>
-      <c r="B12" s="21"/>
+      <c r="B12" s="24"/>
       <c r="C12" s="12"/>
       <c r="D12" s="15"/>
       <c r="E12" s="10"/>
@@ -1050,22 +1062,21 @@
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
       <c r="K12" s="12"/>
-      <c r="L12" s="15"/>
+      <c r="L12" s="25"/>
       <c r="M12" s="10"/>
       <c r="N12" s="12"/>
-      <c r="O12" s="23">
+      <c r="O12" s="15"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="27">
         <v>0.0</v>
       </c>
-      <c r="P12" s="23">
+      <c r="R12" s="27">
         <v>0.0</v>
       </c>
-      <c r="Q12" s="23">
+      <c r="S12" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R12" s="7"/>
-      <c r="S12" s="7"/>
-      <c r="T12" s="7"/>
       <c r="U12" s="7"/>
       <c r="V12" s="7"/>
       <c r="W12" s="7"/>
@@ -1074,10 +1085,10 @@
       <c r="Z12" s="7"/>
     </row>
     <row r="13" ht="18.0" customHeight="1">
-      <c r="A13" s="20">
+      <c r="A13" s="23">
         <v>5.0</v>
       </c>
-      <c r="B13" s="21"/>
+      <c r="B13" s="24"/>
       <c r="C13" s="12"/>
       <c r="D13" s="15"/>
       <c r="E13" s="10"/>
@@ -1087,22 +1098,21 @@
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
       <c r="K13" s="12"/>
-      <c r="L13" s="15"/>
+      <c r="L13" s="25"/>
       <c r="M13" s="10"/>
       <c r="N13" s="12"/>
-      <c r="O13" s="23">
+      <c r="O13" s="15"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="27">
         <v>0.0</v>
       </c>
-      <c r="P13" s="23">
+      <c r="R13" s="27">
         <v>0.0</v>
       </c>
-      <c r="Q13" s="23">
+      <c r="S13" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R13" s="7"/>
-      <c r="S13" s="7"/>
-      <c r="T13" s="7"/>
       <c r="U13" s="7"/>
       <c r="V13" s="7"/>
       <c r="W13" s="7"/>
@@ -1111,10 +1121,10 @@
       <c r="Z13" s="7"/>
     </row>
     <row r="14" ht="18.0" customHeight="1">
-      <c r="A14" s="20">
+      <c r="A14" s="23">
         <v>6.0</v>
       </c>
-      <c r="B14" s="21"/>
+      <c r="B14" s="24"/>
       <c r="C14" s="12"/>
       <c r="D14" s="15"/>
       <c r="E14" s="10"/>
@@ -1124,22 +1134,21 @@
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
       <c r="K14" s="12"/>
-      <c r="L14" s="15"/>
+      <c r="L14" s="25"/>
       <c r="M14" s="10"/>
       <c r="N14" s="12"/>
-      <c r="O14" s="23">
+      <c r="O14" s="15"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="27">
         <v>0.0</v>
       </c>
-      <c r="P14" s="23">
+      <c r="R14" s="27">
         <v>0.0</v>
       </c>
-      <c r="Q14" s="23">
+      <c r="S14" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R14" s="7"/>
-      <c r="S14" s="7"/>
-      <c r="T14" s="7"/>
       <c r="U14" s="7"/>
       <c r="V14" s="7"/>
       <c r="W14" s="7"/>
@@ -1148,10 +1157,10 @@
       <c r="Z14" s="7"/>
     </row>
     <row r="15" ht="18.0" customHeight="1">
-      <c r="A15" s="20">
+      <c r="A15" s="23">
         <v>7.0</v>
       </c>
-      <c r="B15" s="21"/>
+      <c r="B15" s="24"/>
       <c r="C15" s="12"/>
       <c r="D15" s="15"/>
       <c r="E15" s="10"/>
@@ -1161,22 +1170,21 @@
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
       <c r="K15" s="12"/>
-      <c r="L15" s="15"/>
+      <c r="L15" s="25"/>
       <c r="M15" s="10"/>
       <c r="N15" s="12"/>
-      <c r="O15" s="23">
+      <c r="O15" s="15"/>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="27">
         <v>0.0</v>
       </c>
-      <c r="P15" s="23">
+      <c r="R15" s="27">
         <v>0.0</v>
       </c>
-      <c r="Q15" s="23">
+      <c r="S15" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R15" s="7"/>
-      <c r="S15" s="7"/>
-      <c r="T15" s="7"/>
       <c r="U15" s="7"/>
       <c r="V15" s="7"/>
       <c r="W15" s="7"/>
@@ -1185,10 +1193,10 @@
       <c r="Z15" s="7"/>
     </row>
     <row r="16" ht="18.0" customHeight="1">
-      <c r="A16" s="20">
+      <c r="A16" s="23">
         <v>8.0</v>
       </c>
-      <c r="B16" s="21"/>
+      <c r="B16" s="24"/>
       <c r="C16" s="12"/>
       <c r="D16" s="15"/>
       <c r="E16" s="10"/>
@@ -1198,22 +1206,21 @@
       <c r="I16" s="10"/>
       <c r="J16" s="10"/>
       <c r="K16" s="12"/>
-      <c r="L16" s="15"/>
+      <c r="L16" s="25"/>
       <c r="M16" s="10"/>
       <c r="N16" s="12"/>
-      <c r="O16" s="23">
+      <c r="O16" s="15"/>
+      <c r="P16" s="12"/>
+      <c r="Q16" s="27">
         <v>0.0</v>
       </c>
-      <c r="P16" s="23">
+      <c r="R16" s="27">
         <v>0.0</v>
       </c>
-      <c r="Q16" s="23">
+      <c r="S16" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R16" s="7"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
       <c r="U16" s="7"/>
       <c r="V16" s="7"/>
       <c r="W16" s="7"/>
@@ -1222,10 +1229,10 @@
       <c r="Z16" s="7"/>
     </row>
     <row r="17" ht="18.0" customHeight="1">
-      <c r="A17" s="20">
+      <c r="A17" s="23">
         <v>9.0</v>
       </c>
-      <c r="B17" s="21"/>
+      <c r="B17" s="24"/>
       <c r="C17" s="12"/>
       <c r="D17" s="15"/>
       <c r="E17" s="10"/>
@@ -1235,22 +1242,21 @@
       <c r="I17" s="10"/>
       <c r="J17" s="10"/>
       <c r="K17" s="12"/>
-      <c r="L17" s="15"/>
+      <c r="L17" s="25"/>
       <c r="M17" s="10"/>
       <c r="N17" s="12"/>
-      <c r="O17" s="23">
+      <c r="O17" s="15"/>
+      <c r="P17" s="12"/>
+      <c r="Q17" s="27">
         <v>0.0</v>
       </c>
-      <c r="P17" s="23">
+      <c r="R17" s="27">
         <v>0.0</v>
       </c>
-      <c r="Q17" s="23">
+      <c r="S17" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R17" s="7"/>
-      <c r="S17" s="7"/>
-      <c r="T17" s="7"/>
       <c r="U17" s="7"/>
       <c r="V17" s="7"/>
       <c r="W17" s="7"/>
@@ -1259,10 +1265,10 @@
       <c r="Z17" s="7"/>
     </row>
     <row r="18" ht="18.0" customHeight="1">
-      <c r="A18" s="20">
+      <c r="A18" s="23">
         <v>10.0</v>
       </c>
-      <c r="B18" s="21"/>
+      <c r="B18" s="24"/>
       <c r="C18" s="12"/>
       <c r="D18" s="15"/>
       <c r="E18" s="10"/>
@@ -1272,22 +1278,21 @@
       <c r="I18" s="10"/>
       <c r="J18" s="10"/>
       <c r="K18" s="12"/>
-      <c r="L18" s="15"/>
+      <c r="L18" s="25"/>
       <c r="M18" s="10"/>
       <c r="N18" s="12"/>
-      <c r="O18" s="23">
+      <c r="O18" s="15"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="27">
         <v>0.0</v>
       </c>
-      <c r="P18" s="23">
+      <c r="R18" s="27">
         <v>0.0</v>
       </c>
-      <c r="Q18" s="23">
+      <c r="S18" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R18" s="7"/>
-      <c r="S18" s="7"/>
-      <c r="T18" s="7"/>
       <c r="U18" s="7"/>
       <c r="V18" s="7"/>
       <c r="W18" s="7"/>
@@ -1296,10 +1301,10 @@
       <c r="Z18" s="7"/>
     </row>
     <row r="19" ht="18.0" customHeight="1">
-      <c r="A19" s="20">
+      <c r="A19" s="23">
         <v>11.0</v>
       </c>
-      <c r="B19" s="21"/>
+      <c r="B19" s="24"/>
       <c r="C19" s="12"/>
       <c r="D19" s="15"/>
       <c r="E19" s="10"/>
@@ -1309,22 +1314,21 @@
       <c r="I19" s="10"/>
       <c r="J19" s="10"/>
       <c r="K19" s="12"/>
-      <c r="L19" s="15"/>
+      <c r="L19" s="25"/>
       <c r="M19" s="10"/>
       <c r="N19" s="12"/>
-      <c r="O19" s="23">
+      <c r="O19" s="15"/>
+      <c r="P19" s="12"/>
+      <c r="Q19" s="27">
         <v>0.0</v>
       </c>
-      <c r="P19" s="23">
+      <c r="R19" s="27">
         <v>0.0</v>
       </c>
-      <c r="Q19" s="23">
+      <c r="S19" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R19" s="7"/>
-      <c r="S19" s="7"/>
-      <c r="T19" s="7"/>
       <c r="U19" s="7"/>
       <c r="V19" s="7"/>
       <c r="W19" s="7"/>
@@ -1333,10 +1337,10 @@
       <c r="Z19" s="7"/>
     </row>
     <row r="20" ht="18.0" customHeight="1">
-      <c r="A20" s="20">
+      <c r="A20" s="23">
         <v>12.0</v>
       </c>
-      <c r="B20" s="21"/>
+      <c r="B20" s="24"/>
       <c r="C20" s="12"/>
       <c r="D20" s="15"/>
       <c r="E20" s="10"/>
@@ -1346,22 +1350,21 @@
       <c r="I20" s="10"/>
       <c r="J20" s="10"/>
       <c r="K20" s="12"/>
-      <c r="L20" s="15"/>
+      <c r="L20" s="25"/>
       <c r="M20" s="10"/>
       <c r="N20" s="12"/>
-      <c r="O20" s="23">
+      <c r="O20" s="15"/>
+      <c r="P20" s="12"/>
+      <c r="Q20" s="27">
         <v>0.0</v>
       </c>
-      <c r="P20" s="23">
+      <c r="R20" s="27">
         <v>0.0</v>
       </c>
-      <c r="Q20" s="23">
+      <c r="S20" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R20" s="7"/>
-      <c r="S20" s="7"/>
-      <c r="T20" s="7"/>
       <c r="U20" s="7"/>
       <c r="V20" s="7"/>
       <c r="W20" s="7"/>
@@ -1370,10 +1373,10 @@
       <c r="Z20" s="7"/>
     </row>
     <row r="21" ht="18.0" customHeight="1">
-      <c r="A21" s="20">
+      <c r="A21" s="23">
         <v>13.0</v>
       </c>
-      <c r="B21" s="21"/>
+      <c r="B21" s="24"/>
       <c r="C21" s="12"/>
       <c r="D21" s="15"/>
       <c r="E21" s="10"/>
@@ -1383,22 +1386,21 @@
       <c r="I21" s="10"/>
       <c r="J21" s="10"/>
       <c r="K21" s="12"/>
-      <c r="L21" s="15"/>
+      <c r="L21" s="25"/>
       <c r="M21" s="10"/>
       <c r="N21" s="12"/>
-      <c r="O21" s="23">
+      <c r="O21" s="15"/>
+      <c r="P21" s="12"/>
+      <c r="Q21" s="27">
         <v>0.0</v>
       </c>
-      <c r="P21" s="23">
+      <c r="R21" s="27">
         <v>0.0</v>
       </c>
-      <c r="Q21" s="23">
+      <c r="S21" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R21" s="7"/>
-      <c r="S21" s="7"/>
-      <c r="T21" s="7"/>
       <c r="U21" s="7"/>
       <c r="V21" s="7"/>
       <c r="W21" s="7"/>
@@ -1407,10 +1409,10 @@
       <c r="Z21" s="7"/>
     </row>
     <row r="22" ht="18.0" customHeight="1">
-      <c r="A22" s="20">
+      <c r="A22" s="23">
         <v>14.0</v>
       </c>
-      <c r="B22" s="21"/>
+      <c r="B22" s="24"/>
       <c r="C22" s="12"/>
       <c r="D22" s="15"/>
       <c r="E22" s="10"/>
@@ -1420,22 +1422,21 @@
       <c r="I22" s="10"/>
       <c r="J22" s="10"/>
       <c r="K22" s="12"/>
-      <c r="L22" s="15"/>
+      <c r="L22" s="25"/>
       <c r="M22" s="10"/>
       <c r="N22" s="12"/>
-      <c r="O22" s="23">
+      <c r="O22" s="15"/>
+      <c r="P22" s="12"/>
+      <c r="Q22" s="27">
         <v>0.0</v>
       </c>
-      <c r="P22" s="23">
+      <c r="R22" s="27">
         <v>0.0</v>
       </c>
-      <c r="Q22" s="23">
+      <c r="S22" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R22" s="7"/>
-      <c r="S22" s="7"/>
-      <c r="T22" s="7"/>
       <c r="U22" s="7"/>
       <c r="V22" s="7"/>
       <c r="W22" s="7"/>
@@ -1444,10 +1445,10 @@
       <c r="Z22" s="7"/>
     </row>
     <row r="23" ht="18.0" customHeight="1">
-      <c r="A23" s="20">
+      <c r="A23" s="23">
         <v>15.0</v>
       </c>
-      <c r="B23" s="21"/>
+      <c r="B23" s="24"/>
       <c r="C23" s="12"/>
       <c r="D23" s="15"/>
       <c r="E23" s="10"/>
@@ -1457,22 +1458,21 @@
       <c r="I23" s="10"/>
       <c r="J23" s="10"/>
       <c r="K23" s="12"/>
-      <c r="L23" s="15"/>
+      <c r="L23" s="25"/>
       <c r="M23" s="10"/>
       <c r="N23" s="12"/>
-      <c r="O23" s="23">
+      <c r="O23" s="15"/>
+      <c r="P23" s="12"/>
+      <c r="Q23" s="27">
         <v>0.0</v>
       </c>
-      <c r="P23" s="23">
+      <c r="R23" s="27">
         <v>0.0</v>
       </c>
-      <c r="Q23" s="23">
+      <c r="S23" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R23" s="7"/>
-      <c r="S23" s="7"/>
-      <c r="T23" s="7"/>
       <c r="U23" s="7"/>
       <c r="V23" s="7"/>
       <c r="W23" s="7"/>
@@ -1481,10 +1481,10 @@
       <c r="Z23" s="7"/>
     </row>
     <row r="24" ht="18.0" customHeight="1">
-      <c r="A24" s="20">
+      <c r="A24" s="23">
         <v>16.0</v>
       </c>
-      <c r="B24" s="21"/>
+      <c r="B24" s="24"/>
       <c r="C24" s="12"/>
       <c r="D24" s="15"/>
       <c r="E24" s="10"/>
@@ -1494,22 +1494,21 @@
       <c r="I24" s="10"/>
       <c r="J24" s="10"/>
       <c r="K24" s="12"/>
-      <c r="L24" s="15"/>
+      <c r="L24" s="25"/>
       <c r="M24" s="10"/>
       <c r="N24" s="12"/>
-      <c r="O24" s="23">
+      <c r="O24" s="15"/>
+      <c r="P24" s="12"/>
+      <c r="Q24" s="27">
         <v>0.0</v>
       </c>
-      <c r="P24" s="23">
+      <c r="R24" s="27">
         <v>0.0</v>
       </c>
-      <c r="Q24" s="23">
+      <c r="S24" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R24" s="7"/>
-      <c r="S24" s="7"/>
-      <c r="T24" s="7"/>
       <c r="U24" s="7"/>
       <c r="V24" s="7"/>
       <c r="W24" s="7"/>
@@ -1518,10 +1517,10 @@
       <c r="Z24" s="7"/>
     </row>
     <row r="25" ht="18.0" customHeight="1">
-      <c r="A25" s="20">
+      <c r="A25" s="23">
         <v>17.0</v>
       </c>
-      <c r="B25" s="21"/>
+      <c r="B25" s="24"/>
       <c r="C25" s="12"/>
       <c r="D25" s="15"/>
       <c r="E25" s="10"/>
@@ -1531,22 +1530,21 @@
       <c r="I25" s="10"/>
       <c r="J25" s="10"/>
       <c r="K25" s="12"/>
-      <c r="L25" s="15"/>
+      <c r="L25" s="25"/>
       <c r="M25" s="10"/>
       <c r="N25" s="12"/>
-      <c r="O25" s="23">
+      <c r="O25" s="15"/>
+      <c r="P25" s="12"/>
+      <c r="Q25" s="27">
         <v>0.0</v>
       </c>
-      <c r="P25" s="23">
+      <c r="R25" s="27">
         <v>0.0</v>
       </c>
-      <c r="Q25" s="23">
+      <c r="S25" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R25" s="7"/>
-      <c r="S25" s="7"/>
-      <c r="T25" s="7"/>
       <c r="U25" s="7"/>
       <c r="V25" s="7"/>
       <c r="W25" s="7"/>
@@ -1555,10 +1553,10 @@
       <c r="Z25" s="7"/>
     </row>
     <row r="26" ht="18.0" customHeight="1">
-      <c r="A26" s="20">
+      <c r="A26" s="23">
         <v>18.0</v>
       </c>
-      <c r="B26" s="21"/>
+      <c r="B26" s="24"/>
       <c r="C26" s="12"/>
       <c r="D26" s="15"/>
       <c r="E26" s="10"/>
@@ -1568,22 +1566,21 @@
       <c r="I26" s="10"/>
       <c r="J26" s="10"/>
       <c r="K26" s="12"/>
-      <c r="L26" s="15"/>
+      <c r="L26" s="25"/>
       <c r="M26" s="10"/>
       <c r="N26" s="12"/>
-      <c r="O26" s="23">
+      <c r="O26" s="15"/>
+      <c r="P26" s="12"/>
+      <c r="Q26" s="27">
         <v>0.0</v>
       </c>
-      <c r="P26" s="23">
+      <c r="R26" s="27">
         <v>0.0</v>
       </c>
-      <c r="Q26" s="23">
+      <c r="S26" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R26" s="7"/>
-      <c r="S26" s="7"/>
-      <c r="T26" s="7"/>
       <c r="U26" s="7"/>
       <c r="V26" s="7"/>
       <c r="W26" s="7"/>
@@ -1592,10 +1589,10 @@
       <c r="Z26" s="7"/>
     </row>
     <row r="27" ht="18.0" customHeight="1">
-      <c r="A27" s="20">
+      <c r="A27" s="23">
         <v>19.0</v>
       </c>
-      <c r="B27" s="21"/>
+      <c r="B27" s="24"/>
       <c r="C27" s="12"/>
       <c r="D27" s="15"/>
       <c r="E27" s="10"/>
@@ -1605,22 +1602,21 @@
       <c r="I27" s="10"/>
       <c r="J27" s="10"/>
       <c r="K27" s="12"/>
-      <c r="L27" s="15"/>
+      <c r="L27" s="25"/>
       <c r="M27" s="10"/>
       <c r="N27" s="12"/>
-      <c r="O27" s="23">
+      <c r="O27" s="15"/>
+      <c r="P27" s="12"/>
+      <c r="Q27" s="27">
         <v>0.0</v>
       </c>
-      <c r="P27" s="23">
+      <c r="R27" s="27">
         <v>0.0</v>
       </c>
-      <c r="Q27" s="23">
+      <c r="S27" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R27" s="7"/>
-      <c r="S27" s="7"/>
-      <c r="T27" s="7"/>
       <c r="U27" s="7"/>
       <c r="V27" s="7"/>
       <c r="W27" s="7"/>
@@ -1629,10 +1625,10 @@
       <c r="Z27" s="7"/>
     </row>
     <row r="28" ht="18.0" customHeight="1">
-      <c r="A28" s="20">
+      <c r="A28" s="23">
         <v>20.0</v>
       </c>
-      <c r="B28" s="21"/>
+      <c r="B28" s="24"/>
       <c r="C28" s="12"/>
       <c r="D28" s="15"/>
       <c r="E28" s="10"/>
@@ -1642,22 +1638,21 @@
       <c r="I28" s="10"/>
       <c r="J28" s="10"/>
       <c r="K28" s="12"/>
-      <c r="L28" s="15"/>
+      <c r="L28" s="25"/>
       <c r="M28" s="10"/>
       <c r="N28" s="12"/>
-      <c r="O28" s="23">
+      <c r="O28" s="15"/>
+      <c r="P28" s="12"/>
+      <c r="Q28" s="27">
         <v>0.0</v>
       </c>
-      <c r="P28" s="23">
+      <c r="R28" s="27">
         <v>0.0</v>
       </c>
-      <c r="Q28" s="23">
+      <c r="S28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R28" s="7"/>
-      <c r="S28" s="7"/>
-      <c r="T28" s="7"/>
       <c r="U28" s="7"/>
       <c r="V28" s="7"/>
       <c r="W28" s="7"/>
@@ -1666,25 +1661,25 @@
       <c r="Z28" s="7"/>
     </row>
     <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="24" t="s">
-        <v>15</v>
+      <c r="A29" s="28" t="s">
+        <v>16</v>
       </c>
-      <c r="B29" s="25"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="25"/>
-      <c r="I29" s="25"/>
-      <c r="J29" s="25"/>
-      <c r="K29" s="25"/>
-      <c r="L29" s="25"/>
-      <c r="M29" s="25"/>
-      <c r="N29" s="25"/>
-      <c r="O29" s="25"/>
-      <c r="P29" s="25"/>
-      <c r="Q29" s="25"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="29"/>
+      <c r="O29" s="29"/>
+      <c r="P29" s="29"/>
+      <c r="Q29" s="29"/>
       <c r="R29" s="7"/>
       <c r="S29" s="7"/>
       <c r="T29" s="7"/>
@@ -1731,15 +1726,15 @@
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
-      <c r="H31" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="I31" s="27" t="s">
+      <c r="H31" s="30" t="s">
         <v>17</v>
       </c>
+      <c r="I31" s="31" t="s">
+        <v>18</v>
+      </c>
       <c r="J31" s="12"/>
-      <c r="K31" s="28">
-        <v>5000.0</v>
+      <c r="K31" s="32">
+        <v>10000.0</v>
       </c>
       <c r="L31" s="7"/>
       <c r="M31" s="7"/>
@@ -1762,15 +1757,15 @@
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
-      <c r="E32" s="29"/>
+      <c r="E32" s="33"/>
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="31" t="s">
-        <v>18</v>
+      <c r="H32" s="34"/>
+      <c r="I32" s="35" t="s">
+        <v>19</v>
       </c>
       <c r="J32" s="12"/>
-      <c r="K32" s="28"/>
+      <c r="K32" s="36"/>
       <c r="L32" s="7"/>
       <c r="M32" s="7"/>
       <c r="N32" s="7"/>
@@ -1795,13 +1790,13 @@
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="31" t="s">
-        <v>19</v>
+      <c r="H33" s="34"/>
+      <c r="I33" s="35" t="s">
+        <v>20</v>
       </c>
       <c r="J33" s="12"/>
-      <c r="K33" s="28">
-        <f>SUM(Q9:Q28)</f>
+      <c r="K33" s="36">
+        <f>SUM(S9:S28)</f>
         <v>0</v>
       </c>
       <c r="L33" s="7"/>
@@ -1828,14 +1823,14 @@
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
       <c r="G34" s="7"/>
-      <c r="H34" s="32"/>
-      <c r="I34" s="31" t="s">
-        <v>20</v>
+      <c r="H34" s="37"/>
+      <c r="I34" s="35" t="s">
+        <v>21</v>
       </c>
       <c r="J34" s="12"/>
-      <c r="K34" s="28">
+      <c r="K34" s="36">
         <f>K31-(K32+K33)</f>
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="L34" s="7"/>
       <c r="M34" s="7"/>
@@ -1914,14 +1909,14 @@
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
-      <c r="E37" s="33" t="s">
-        <v>21</v>
+      <c r="E37" s="38" t="s">
+        <v>22</v>
       </c>
-      <c r="F37" s="25"/>
-      <c r="G37" s="34"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="39"/>
       <c r="H37" s="7"/>
-      <c r="I37" s="35" t="s">
-        <v>22</v>
+      <c r="I37" s="40" t="s">
+        <v>23</v>
       </c>
       <c r="J37" s="10"/>
       <c r="K37" s="10"/>
@@ -1946,12 +1941,12 @@
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
-      <c r="E38" s="36"/>
-      <c r="F38" s="37"/>
-      <c r="G38" s="38"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="21"/>
       <c r="H38" s="7"/>
       <c r="I38" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J38" s="10"/>
       <c r="K38" s="12"/>
@@ -28910,40 +28905,118 @@
       <c r="Z1000" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="107">
+  <mergeCells count="128">
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="D12:G12"/>
     <mergeCell ref="H12:K12"/>
-    <mergeCell ref="L12:N12"/>
     <mergeCell ref="D13:G13"/>
     <mergeCell ref="H13:K13"/>
+    <mergeCell ref="L12:N12"/>
     <mergeCell ref="L13:N13"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="D14:G14"/>
     <mergeCell ref="H14:K14"/>
-    <mergeCell ref="L14:N14"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="D15:G15"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="H8:K8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="H9:K9"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="H10:K10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="D1:O1"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="O22:P22"/>
+    <mergeCell ref="O23:P23"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:G24"/>
+    <mergeCell ref="H24:K24"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="H25:K25"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="H26:K26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="A29:Q29"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="H16:K16"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="H17:K17"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="H18:K18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="H20:K20"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="H21:K21"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="H22:K22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="H28:K28"/>
+    <mergeCell ref="E37:G38"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="L38:N38"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="L39:N39"/>
+    <mergeCell ref="I37:N37"/>
+    <mergeCell ref="H27:K27"/>
+    <mergeCell ref="H31:H34"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="H23:K23"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="O14:P14"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="O18:P18"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="G3:I3"/>
-    <mergeCell ref="K3:M3"/>
     <mergeCell ref="N3:P3"/>
     <mergeCell ref="G4:I4"/>
-    <mergeCell ref="A7:Q7"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="A7:S7"/>
+    <mergeCell ref="D1:P1"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:G11"/>
     <mergeCell ref="H11:K11"/>
     <mergeCell ref="L11:N11"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="O13:P13"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="D8:G8"/>
@@ -28951,77 +29024,20 @@
     <mergeCell ref="D9:G9"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="D10:G10"/>
+    <mergeCell ref="N4:P4"/>
     <mergeCell ref="H15:K15"/>
-    <mergeCell ref="L15:N15"/>
     <mergeCell ref="H19:K19"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:G24"/>
-    <mergeCell ref="H24:K24"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="H25:K25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="H26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="A29:Q29"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:G16"/>
-    <mergeCell ref="H16:K16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="H17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="H18:K18"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="H20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="H21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="H23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="H22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="H28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="E37:G38"/>
-    <mergeCell ref="I37:N37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="L38:N38"/>
-    <mergeCell ref="E39:G39"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="L39:N39"/>
-    <mergeCell ref="H27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="H31:H34"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="H8:K8"/>
+    <mergeCell ref="H9:K9"/>
+    <mergeCell ref="H10:K10"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="L10:N10"/>
   </mergeCells>
   <printOptions/>
-  <pageMargins bottom="0.41386138613861384" footer="0.0" header="0.0" left="0.5881188118811881" right="0.5881188118811881" top="0.41386138613861384"/>
-  <pageSetup scale="80" orientation="landscape"/>
+  <pageMargins bottom="0.41386138613861384" footer="0.0" header="0.0" left="0.3702970297029703" right="0.3267326732673267" top="0.41386138613861384"/>
+  <pageSetup scale="75" orientation="landscape"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/DocumentosProceso/Comprobación para el reembolso de fondo fijo de CEDIS.xlsx
+++ b/DocumentosProceso/Comprobación para el reembolso de fondo fijo de CEDIS.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Comprobación de Gastos" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Comprobación de Gastos" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName localSheetId="0" name="Print_Area">'Comprobación de Gastos'!$A$1:$Q$36</definedName>
@@ -42,7 +42,7 @@
     <t>Fecha comprobante</t>
   </si>
   <si>
-    <t>No. de comprobante o factura</t>
+    <t>Folio fiscal</t>
   </si>
   <si>
     <t>Proveedor</t>
@@ -332,7 +332,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -387,6 +387,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="10" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="12" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="13" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
@@ -472,6 +475,10 @@
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -903,17 +910,17 @@
         <v>8</v>
       </c>
       <c r="C8" s="21"/>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
       <c r="G8" s="21"/>
       <c r="H8" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="22"/>
-      <c r="J8" s="22"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
       <c r="K8" s="21"/>
       <c r="L8" s="9" t="s">
         <v>11</v>
@@ -941,10 +948,10 @@
       <c r="Z8" s="7"/>
     </row>
     <row r="9" ht="18.0" customHeight="1">
-      <c r="A9" s="23">
+      <c r="A9" s="24">
         <v>1.0</v>
       </c>
-      <c r="B9" s="24"/>
+      <c r="B9" s="25"/>
       <c r="C9" s="12"/>
       <c r="D9" s="15"/>
       <c r="E9" s="10"/>
@@ -954,18 +961,18 @@
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
       <c r="K9" s="12"/>
-      <c r="L9" s="25"/>
+      <c r="L9" s="26"/>
       <c r="M9" s="10"/>
       <c r="N9" s="12"/>
       <c r="O9" s="15"/>
       <c r="P9" s="12"/>
-      <c r="Q9" s="26">
+      <c r="Q9" s="27">
         <v>0.0</v>
       </c>
-      <c r="R9" s="26">
+      <c r="R9" s="27">
         <v>0.0</v>
       </c>
-      <c r="S9" s="27">
+      <c r="S9" s="28">
         <f t="shared" ref="S9:S28" si="1">Q9+R9</f>
         <v>0</v>
       </c>
@@ -977,10 +984,10 @@
       <c r="Z9" s="7"/>
     </row>
     <row r="10" ht="18.0" customHeight="1">
-      <c r="A10" s="23">
+      <c r="A10" s="24">
         <v>2.0</v>
       </c>
-      <c r="B10" s="24"/>
+      <c r="B10" s="25"/>
       <c r="C10" s="12"/>
       <c r="D10" s="15"/>
       <c r="E10" s="10"/>
@@ -990,18 +997,18 @@
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
       <c r="K10" s="12"/>
-      <c r="L10" s="25"/>
+      <c r="L10" s="26"/>
       <c r="M10" s="10"/>
       <c r="N10" s="12"/>
       <c r="O10" s="15"/>
       <c r="P10" s="12"/>
-      <c r="Q10" s="27">
+      <c r="Q10" s="28">
         <v>0.0</v>
       </c>
-      <c r="R10" s="27">
+      <c r="R10" s="28">
         <v>0.0</v>
       </c>
-      <c r="S10" s="27">
+      <c r="S10" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1013,10 +1020,10 @@
       <c r="Z10" s="7"/>
     </row>
     <row r="11" ht="18.0" customHeight="1">
-      <c r="A11" s="23">
+      <c r="A11" s="24">
         <v>3.0</v>
       </c>
-      <c r="B11" s="24"/>
+      <c r="B11" s="25"/>
       <c r="C11" s="12"/>
       <c r="D11" s="15"/>
       <c r="E11" s="10"/>
@@ -1026,18 +1033,18 @@
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
       <c r="K11" s="12"/>
-      <c r="L11" s="25"/>
+      <c r="L11" s="26"/>
       <c r="M11" s="10"/>
       <c r="N11" s="12"/>
       <c r="O11" s="15"/>
       <c r="P11" s="12"/>
-      <c r="Q11" s="27">
+      <c r="Q11" s="28">
         <v>0.0</v>
       </c>
-      <c r="R11" s="27">
+      <c r="R11" s="28">
         <v>0.0</v>
       </c>
-      <c r="S11" s="27">
+      <c r="S11" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1049,10 +1056,10 @@
       <c r="Z11" s="7"/>
     </row>
     <row r="12" ht="18.0" customHeight="1">
-      <c r="A12" s="23">
+      <c r="A12" s="24">
         <v>4.0</v>
       </c>
-      <c r="B12" s="24"/>
+      <c r="B12" s="25"/>
       <c r="C12" s="12"/>
       <c r="D12" s="15"/>
       <c r="E12" s="10"/>
@@ -1062,18 +1069,18 @@
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
       <c r="K12" s="12"/>
-      <c r="L12" s="25"/>
+      <c r="L12" s="26"/>
       <c r="M12" s="10"/>
       <c r="N12" s="12"/>
       <c r="O12" s="15"/>
       <c r="P12" s="12"/>
-      <c r="Q12" s="27">
+      <c r="Q12" s="28">
         <v>0.0</v>
       </c>
-      <c r="R12" s="27">
+      <c r="R12" s="28">
         <v>0.0</v>
       </c>
-      <c r="S12" s="27">
+      <c r="S12" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1085,10 +1092,10 @@
       <c r="Z12" s="7"/>
     </row>
     <row r="13" ht="18.0" customHeight="1">
-      <c r="A13" s="23">
+      <c r="A13" s="24">
         <v>5.0</v>
       </c>
-      <c r="B13" s="24"/>
+      <c r="B13" s="25"/>
       <c r="C13" s="12"/>
       <c r="D13" s="15"/>
       <c r="E13" s="10"/>
@@ -1098,18 +1105,18 @@
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
       <c r="K13" s="12"/>
-      <c r="L13" s="25"/>
+      <c r="L13" s="26"/>
       <c r="M13" s="10"/>
       <c r="N13" s="12"/>
       <c r="O13" s="15"/>
       <c r="P13" s="12"/>
-      <c r="Q13" s="27">
+      <c r="Q13" s="28">
         <v>0.0</v>
       </c>
-      <c r="R13" s="27">
+      <c r="R13" s="28">
         <v>0.0</v>
       </c>
-      <c r="S13" s="27">
+      <c r="S13" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1121,10 +1128,10 @@
       <c r="Z13" s="7"/>
     </row>
     <row r="14" ht="18.0" customHeight="1">
-      <c r="A14" s="23">
+      <c r="A14" s="24">
         <v>6.0</v>
       </c>
-      <c r="B14" s="24"/>
+      <c r="B14" s="25"/>
       <c r="C14" s="12"/>
       <c r="D14" s="15"/>
       <c r="E14" s="10"/>
@@ -1134,18 +1141,18 @@
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
       <c r="K14" s="12"/>
-      <c r="L14" s="25"/>
+      <c r="L14" s="26"/>
       <c r="M14" s="10"/>
       <c r="N14" s="12"/>
       <c r="O14" s="15"/>
       <c r="P14" s="12"/>
-      <c r="Q14" s="27">
+      <c r="Q14" s="28">
         <v>0.0</v>
       </c>
-      <c r="R14" s="27">
+      <c r="R14" s="28">
         <v>0.0</v>
       </c>
-      <c r="S14" s="27">
+      <c r="S14" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1157,10 +1164,10 @@
       <c r="Z14" s="7"/>
     </row>
     <row r="15" ht="18.0" customHeight="1">
-      <c r="A15" s="23">
+      <c r="A15" s="24">
         <v>7.0</v>
       </c>
-      <c r="B15" s="24"/>
+      <c r="B15" s="25"/>
       <c r="C15" s="12"/>
       <c r="D15" s="15"/>
       <c r="E15" s="10"/>
@@ -1170,18 +1177,18 @@
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
       <c r="K15" s="12"/>
-      <c r="L15" s="25"/>
+      <c r="L15" s="26"/>
       <c r="M15" s="10"/>
       <c r="N15" s="12"/>
       <c r="O15" s="15"/>
       <c r="P15" s="12"/>
-      <c r="Q15" s="27">
+      <c r="Q15" s="28">
         <v>0.0</v>
       </c>
-      <c r="R15" s="27">
+      <c r="R15" s="28">
         <v>0.0</v>
       </c>
-      <c r="S15" s="27">
+      <c r="S15" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1193,10 +1200,10 @@
       <c r="Z15" s="7"/>
     </row>
     <row r="16" ht="18.0" customHeight="1">
-      <c r="A16" s="23">
+      <c r="A16" s="24">
         <v>8.0</v>
       </c>
-      <c r="B16" s="24"/>
+      <c r="B16" s="25"/>
       <c r="C16" s="12"/>
       <c r="D16" s="15"/>
       <c r="E16" s="10"/>
@@ -1206,18 +1213,18 @@
       <c r="I16" s="10"/>
       <c r="J16" s="10"/>
       <c r="K16" s="12"/>
-      <c r="L16" s="25"/>
+      <c r="L16" s="26"/>
       <c r="M16" s="10"/>
       <c r="N16" s="12"/>
       <c r="O16" s="15"/>
       <c r="P16" s="12"/>
-      <c r="Q16" s="27">
+      <c r="Q16" s="28">
         <v>0.0</v>
       </c>
-      <c r="R16" s="27">
+      <c r="R16" s="28">
         <v>0.0</v>
       </c>
-      <c r="S16" s="27">
+      <c r="S16" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1229,10 +1236,10 @@
       <c r="Z16" s="7"/>
     </row>
     <row r="17" ht="18.0" customHeight="1">
-      <c r="A17" s="23">
+      <c r="A17" s="24">
         <v>9.0</v>
       </c>
-      <c r="B17" s="24"/>
+      <c r="B17" s="25"/>
       <c r="C17" s="12"/>
       <c r="D17" s="15"/>
       <c r="E17" s="10"/>
@@ -1242,18 +1249,18 @@
       <c r="I17" s="10"/>
       <c r="J17" s="10"/>
       <c r="K17" s="12"/>
-      <c r="L17" s="25"/>
+      <c r="L17" s="26"/>
       <c r="M17" s="10"/>
       <c r="N17" s="12"/>
       <c r="O17" s="15"/>
       <c r="P17" s="12"/>
-      <c r="Q17" s="27">
+      <c r="Q17" s="28">
         <v>0.0</v>
       </c>
-      <c r="R17" s="27">
+      <c r="R17" s="28">
         <v>0.0</v>
       </c>
-      <c r="S17" s="27">
+      <c r="S17" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1265,10 +1272,10 @@
       <c r="Z17" s="7"/>
     </row>
     <row r="18" ht="18.0" customHeight="1">
-      <c r="A18" s="23">
+      <c r="A18" s="24">
         <v>10.0</v>
       </c>
-      <c r="B18" s="24"/>
+      <c r="B18" s="25"/>
       <c r="C18" s="12"/>
       <c r="D18" s="15"/>
       <c r="E18" s="10"/>
@@ -1278,18 +1285,18 @@
       <c r="I18" s="10"/>
       <c r="J18" s="10"/>
       <c r="K18" s="12"/>
-      <c r="L18" s="25"/>
+      <c r="L18" s="26"/>
       <c r="M18" s="10"/>
       <c r="N18" s="12"/>
       <c r="O18" s="15"/>
       <c r="P18" s="12"/>
-      <c r="Q18" s="27">
+      <c r="Q18" s="28">
         <v>0.0</v>
       </c>
-      <c r="R18" s="27">
+      <c r="R18" s="28">
         <v>0.0</v>
       </c>
-      <c r="S18" s="27">
+      <c r="S18" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1301,10 +1308,10 @@
       <c r="Z18" s="7"/>
     </row>
     <row r="19" ht="18.0" customHeight="1">
-      <c r="A19" s="23">
+      <c r="A19" s="24">
         <v>11.0</v>
       </c>
-      <c r="B19" s="24"/>
+      <c r="B19" s="25"/>
       <c r="C19" s="12"/>
       <c r="D19" s="15"/>
       <c r="E19" s="10"/>
@@ -1314,18 +1321,18 @@
       <c r="I19" s="10"/>
       <c r="J19" s="10"/>
       <c r="K19" s="12"/>
-      <c r="L19" s="25"/>
+      <c r="L19" s="26"/>
       <c r="M19" s="10"/>
       <c r="N19" s="12"/>
       <c r="O19" s="15"/>
       <c r="P19" s="12"/>
-      <c r="Q19" s="27">
+      <c r="Q19" s="28">
         <v>0.0</v>
       </c>
-      <c r="R19" s="27">
+      <c r="R19" s="28">
         <v>0.0</v>
       </c>
-      <c r="S19" s="27">
+      <c r="S19" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1337,10 +1344,10 @@
       <c r="Z19" s="7"/>
     </row>
     <row r="20" ht="18.0" customHeight="1">
-      <c r="A20" s="23">
+      <c r="A20" s="24">
         <v>12.0</v>
       </c>
-      <c r="B20" s="24"/>
+      <c r="B20" s="25"/>
       <c r="C20" s="12"/>
       <c r="D20" s="15"/>
       <c r="E20" s="10"/>
@@ -1350,18 +1357,18 @@
       <c r="I20" s="10"/>
       <c r="J20" s="10"/>
       <c r="K20" s="12"/>
-      <c r="L20" s="25"/>
+      <c r="L20" s="26"/>
       <c r="M20" s="10"/>
       <c r="N20" s="12"/>
       <c r="O20" s="15"/>
       <c r="P20" s="12"/>
-      <c r="Q20" s="27">
+      <c r="Q20" s="28">
         <v>0.0</v>
       </c>
-      <c r="R20" s="27">
+      <c r="R20" s="28">
         <v>0.0</v>
       </c>
-      <c r="S20" s="27">
+      <c r="S20" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1373,10 +1380,10 @@
       <c r="Z20" s="7"/>
     </row>
     <row r="21" ht="18.0" customHeight="1">
-      <c r="A21" s="23">
+      <c r="A21" s="24">
         <v>13.0</v>
       </c>
-      <c r="B21" s="24"/>
+      <c r="B21" s="25"/>
       <c r="C21" s="12"/>
       <c r="D21" s="15"/>
       <c r="E21" s="10"/>
@@ -1386,18 +1393,18 @@
       <c r="I21" s="10"/>
       <c r="J21" s="10"/>
       <c r="K21" s="12"/>
-      <c r="L21" s="25"/>
+      <c r="L21" s="26"/>
       <c r="M21" s="10"/>
       <c r="N21" s="12"/>
       <c r="O21" s="15"/>
       <c r="P21" s="12"/>
-      <c r="Q21" s="27">
+      <c r="Q21" s="28">
         <v>0.0</v>
       </c>
-      <c r="R21" s="27">
+      <c r="R21" s="28">
         <v>0.0</v>
       </c>
-      <c r="S21" s="27">
+      <c r="S21" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1409,10 +1416,10 @@
       <c r="Z21" s="7"/>
     </row>
     <row r="22" ht="18.0" customHeight="1">
-      <c r="A22" s="23">
+      <c r="A22" s="24">
         <v>14.0</v>
       </c>
-      <c r="B22" s="24"/>
+      <c r="B22" s="25"/>
       <c r="C22" s="12"/>
       <c r="D22" s="15"/>
       <c r="E22" s="10"/>
@@ -1422,18 +1429,18 @@
       <c r="I22" s="10"/>
       <c r="J22" s="10"/>
       <c r="K22" s="12"/>
-      <c r="L22" s="25"/>
+      <c r="L22" s="26"/>
       <c r="M22" s="10"/>
       <c r="N22" s="12"/>
       <c r="O22" s="15"/>
       <c r="P22" s="12"/>
-      <c r="Q22" s="27">
+      <c r="Q22" s="28">
         <v>0.0</v>
       </c>
-      <c r="R22" s="27">
+      <c r="R22" s="28">
         <v>0.0</v>
       </c>
-      <c r="S22" s="27">
+      <c r="S22" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1445,10 +1452,10 @@
       <c r="Z22" s="7"/>
     </row>
     <row r="23" ht="18.0" customHeight="1">
-      <c r="A23" s="23">
+      <c r="A23" s="24">
         <v>15.0</v>
       </c>
-      <c r="B23" s="24"/>
+      <c r="B23" s="25"/>
       <c r="C23" s="12"/>
       <c r="D23" s="15"/>
       <c r="E23" s="10"/>
@@ -1458,18 +1465,18 @@
       <c r="I23" s="10"/>
       <c r="J23" s="10"/>
       <c r="K23" s="12"/>
-      <c r="L23" s="25"/>
+      <c r="L23" s="26"/>
       <c r="M23" s="10"/>
       <c r="N23" s="12"/>
       <c r="O23" s="15"/>
       <c r="P23" s="12"/>
-      <c r="Q23" s="27">
+      <c r="Q23" s="28">
         <v>0.0</v>
       </c>
-      <c r="R23" s="27">
+      <c r="R23" s="28">
         <v>0.0</v>
       </c>
-      <c r="S23" s="27">
+      <c r="S23" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1481,10 +1488,10 @@
       <c r="Z23" s="7"/>
     </row>
     <row r="24" ht="18.0" customHeight="1">
-      <c r="A24" s="23">
+      <c r="A24" s="24">
         <v>16.0</v>
       </c>
-      <c r="B24" s="24"/>
+      <c r="B24" s="25"/>
       <c r="C24" s="12"/>
       <c r="D24" s="15"/>
       <c r="E24" s="10"/>
@@ -1494,18 +1501,18 @@
       <c r="I24" s="10"/>
       <c r="J24" s="10"/>
       <c r="K24" s="12"/>
-      <c r="L24" s="25"/>
+      <c r="L24" s="26"/>
       <c r="M24" s="10"/>
       <c r="N24" s="12"/>
       <c r="O24" s="15"/>
       <c r="P24" s="12"/>
-      <c r="Q24" s="27">
+      <c r="Q24" s="28">
         <v>0.0</v>
       </c>
-      <c r="R24" s="27">
+      <c r="R24" s="28">
         <v>0.0</v>
       </c>
-      <c r="S24" s="27">
+      <c r="S24" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1517,10 +1524,10 @@
       <c r="Z24" s="7"/>
     </row>
     <row r="25" ht="18.0" customHeight="1">
-      <c r="A25" s="23">
+      <c r="A25" s="24">
         <v>17.0</v>
       </c>
-      <c r="B25" s="24"/>
+      <c r="B25" s="25"/>
       <c r="C25" s="12"/>
       <c r="D25" s="15"/>
       <c r="E25" s="10"/>
@@ -1530,18 +1537,18 @@
       <c r="I25" s="10"/>
       <c r="J25" s="10"/>
       <c r="K25" s="12"/>
-      <c r="L25" s="25"/>
+      <c r="L25" s="26"/>
       <c r="M25" s="10"/>
       <c r="N25" s="12"/>
       <c r="O25" s="15"/>
       <c r="P25" s="12"/>
-      <c r="Q25" s="27">
+      <c r="Q25" s="28">
         <v>0.0</v>
       </c>
-      <c r="R25" s="27">
+      <c r="R25" s="28">
         <v>0.0</v>
       </c>
-      <c r="S25" s="27">
+      <c r="S25" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1553,10 +1560,10 @@
       <c r="Z25" s="7"/>
     </row>
     <row r="26" ht="18.0" customHeight="1">
-      <c r="A26" s="23">
+      <c r="A26" s="24">
         <v>18.0</v>
       </c>
-      <c r="B26" s="24"/>
+      <c r="B26" s="25"/>
       <c r="C26" s="12"/>
       <c r="D26" s="15"/>
       <c r="E26" s="10"/>
@@ -1566,18 +1573,18 @@
       <c r="I26" s="10"/>
       <c r="J26" s="10"/>
       <c r="K26" s="12"/>
-      <c r="L26" s="25"/>
+      <c r="L26" s="26"/>
       <c r="M26" s="10"/>
       <c r="N26" s="12"/>
       <c r="O26" s="15"/>
       <c r="P26" s="12"/>
-      <c r="Q26" s="27">
+      <c r="Q26" s="28">
         <v>0.0</v>
       </c>
-      <c r="R26" s="27">
+      <c r="R26" s="28">
         <v>0.0</v>
       </c>
-      <c r="S26" s="27">
+      <c r="S26" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1589,10 +1596,10 @@
       <c r="Z26" s="7"/>
     </row>
     <row r="27" ht="18.0" customHeight="1">
-      <c r="A27" s="23">
+      <c r="A27" s="24">
         <v>19.0</v>
       </c>
-      <c r="B27" s="24"/>
+      <c r="B27" s="25"/>
       <c r="C27" s="12"/>
       <c r="D27" s="15"/>
       <c r="E27" s="10"/>
@@ -1602,18 +1609,18 @@
       <c r="I27" s="10"/>
       <c r="J27" s="10"/>
       <c r="K27" s="12"/>
-      <c r="L27" s="25"/>
+      <c r="L27" s="26"/>
       <c r="M27" s="10"/>
       <c r="N27" s="12"/>
       <c r="O27" s="15"/>
       <c r="P27" s="12"/>
-      <c r="Q27" s="27">
+      <c r="Q27" s="28">
         <v>0.0</v>
       </c>
-      <c r="R27" s="27">
+      <c r="R27" s="28">
         <v>0.0</v>
       </c>
-      <c r="S27" s="27">
+      <c r="S27" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1625,10 +1632,10 @@
       <c r="Z27" s="7"/>
     </row>
     <row r="28" ht="18.0" customHeight="1">
-      <c r="A28" s="23">
+      <c r="A28" s="24">
         <v>20.0</v>
       </c>
-      <c r="B28" s="24"/>
+      <c r="B28" s="25"/>
       <c r="C28" s="12"/>
       <c r="D28" s="15"/>
       <c r="E28" s="10"/>
@@ -1638,18 +1645,18 @@
       <c r="I28" s="10"/>
       <c r="J28" s="10"/>
       <c r="K28" s="12"/>
-      <c r="L28" s="25"/>
+      <c r="L28" s="26"/>
       <c r="M28" s="10"/>
       <c r="N28" s="12"/>
       <c r="O28" s="15"/>
       <c r="P28" s="12"/>
-      <c r="Q28" s="27">
+      <c r="Q28" s="28">
         <v>0.0</v>
       </c>
-      <c r="R28" s="27">
+      <c r="R28" s="28">
         <v>0.0</v>
       </c>
-      <c r="S28" s="27">
+      <c r="S28" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1661,25 +1668,25 @@
       <c r="Z28" s="7"/>
     </row>
     <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="29"/>
-      <c r="K29" s="29"/>
-      <c r="L29" s="29"/>
-      <c r="M29" s="29"/>
-      <c r="N29" s="29"/>
-      <c r="O29" s="29"/>
-      <c r="P29" s="29"/>
-      <c r="Q29" s="29"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="30"/>
+      <c r="Q29" s="30"/>
       <c r="R29" s="7"/>
       <c r="S29" s="7"/>
       <c r="T29" s="7"/>
@@ -1726,15 +1733,15 @@
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
-      <c r="H31" s="30" t="s">
+      <c r="H31" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="I31" s="31" t="s">
+      <c r="I31" s="32" t="s">
         <v>18</v>
       </c>
       <c r="J31" s="12"/>
-      <c r="K31" s="32">
-        <v>10000.0</v>
+      <c r="K31" s="33">
+        <v>5000.0</v>
       </c>
       <c r="L31" s="7"/>
       <c r="M31" s="7"/>
@@ -1757,15 +1764,15 @@
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
-      <c r="E32" s="33"/>
+      <c r="E32" s="34"/>
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
-      <c r="H32" s="34"/>
-      <c r="I32" s="35" t="s">
+      <c r="H32" s="35"/>
+      <c r="I32" s="36" t="s">
         <v>19</v>
       </c>
       <c r="J32" s="12"/>
-      <c r="K32" s="36"/>
+      <c r="K32" s="37"/>
       <c r="L32" s="7"/>
       <c r="M32" s="7"/>
       <c r="N32" s="7"/>
@@ -1790,12 +1797,12 @@
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
-      <c r="H33" s="34"/>
-      <c r="I33" s="35" t="s">
+      <c r="H33" s="35"/>
+      <c r="I33" s="36" t="s">
         <v>20</v>
       </c>
       <c r="J33" s="12"/>
-      <c r="K33" s="36">
+      <c r="K33" s="37">
         <f>SUM(S9:S28)</f>
         <v>0</v>
       </c>
@@ -1823,14 +1830,14 @@
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
       <c r="G34" s="7"/>
-      <c r="H34" s="37"/>
-      <c r="I34" s="35" t="s">
+      <c r="H34" s="38"/>
+      <c r="I34" s="36" t="s">
         <v>21</v>
       </c>
       <c r="J34" s="12"/>
-      <c r="K34" s="36">
+      <c r="K34" s="37">
         <f>K31-(K32+K33)</f>
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="L34" s="7"/>
       <c r="M34" s="7"/>
@@ -1909,13 +1916,13 @@
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
-      <c r="E37" s="38" t="s">
+      <c r="E37" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="F37" s="29"/>
-      <c r="G37" s="39"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="40"/>
       <c r="H37" s="7"/>
-      <c r="I37" s="40" t="s">
+      <c r="I37" s="41" t="s">
         <v>23</v>
       </c>
       <c r="J37" s="10"/>
@@ -1941,8 +1948,8 @@
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="22"/>
+      <c r="E38" s="42"/>
+      <c r="F38" s="23"/>
       <c r="G38" s="21"/>
       <c r="H38" s="7"/>
       <c r="I38" s="9" t="s">
@@ -28906,134 +28913,134 @@
     </row>
   </sheetData>
   <mergeCells count="128">
-    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D1:P1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="A7:S7"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="H8:K8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:G9"/>
+    <mergeCell ref="H9:K9"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:G10"/>
+    <mergeCell ref="H10:K10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="H11:K11"/>
     <mergeCell ref="D12:G12"/>
     <mergeCell ref="H12:K12"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="O14:P14"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
     <mergeCell ref="D13:G13"/>
     <mergeCell ref="H13:K13"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="D14:G14"/>
     <mergeCell ref="H14:K14"/>
+    <mergeCell ref="H24:K24"/>
+    <mergeCell ref="H25:K25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="H22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="H23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:P23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:G24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="H31:H34"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="L39:N39"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="E37:G38"/>
+    <mergeCell ref="I37:N37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="L38:N38"/>
+    <mergeCell ref="E39:G39"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="D15:G15"/>
-    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="H15:K15"/>
     <mergeCell ref="L15:N15"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="H18:K18"/>
+    <mergeCell ref="H19:K19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="H16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="H17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="H20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="H21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="D22:G22"/>
     <mergeCell ref="O22:P22"/>
-    <mergeCell ref="O23:P23"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:G24"/>
-    <mergeCell ref="H24:K24"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="H25:K25"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="H27:K27"/>
+    <mergeCell ref="H28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="A29:Q29"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="D26:G26"/>
     <mergeCell ref="H26:K26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="A29:Q29"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="O28:P28"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:G16"/>
-    <mergeCell ref="H16:K16"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="H17:K17"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="H18:K18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="H20:K20"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="H21:K21"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="H22:K22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="H28:K28"/>
-    <mergeCell ref="E37:G38"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="L38:N38"/>
-    <mergeCell ref="E39:G39"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="L39:N39"/>
-    <mergeCell ref="I37:N37"/>
-    <mergeCell ref="H27:K27"/>
-    <mergeCell ref="H31:H34"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="H23:K23"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="O9:P9"/>
-    <mergeCell ref="O10:P10"/>
-    <mergeCell ref="O14:P14"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="A7:S7"/>
-    <mergeCell ref="D1:P1"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:G11"/>
-    <mergeCell ref="H11:K11"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="O12:P12"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:G8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:G9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:G10"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="H15:K15"/>
-    <mergeCell ref="H19:K19"/>
-    <mergeCell ref="H8:K8"/>
-    <mergeCell ref="H9:K9"/>
-    <mergeCell ref="H10:K10"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="O27:P27"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.41386138613861384" footer="0.0" header="0.0" left="0.3702970297029703" right="0.3267326732673267" top="0.41386138613861384"/>
